--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260709.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.89%</t>
+          <t>10.00%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.07%</t>
+          <t>9.21%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.49%</t>
+          <t>7.48%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.35%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.09%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.96%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>80,347</t>
+          <t>52,236</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,61 +1085,61 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>52,236</t>
+          <t>80,347</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>31,768</t>
+          <t>23,226</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,226</t>
+          <t>31,768</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1261,61 +1261,61 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>78,337</t>
+          <t>9,396</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,396</t>
+          <t>13,828</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,828</t>
+          <t>78,337</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1452,51 +1452,51 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>45,373</t>
+          <t>14,007</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>14,007</t>
+          <t>45,373</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>119,055,875</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
